--- a/data/raw/exogenous/anex-IPC-Variacion-jun2025.xlsx
+++ b/data/raw/exogenous/anex-IPC-Variacion-jun2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\Dev\maestria-trabajo-integrador\data\raw\exogenous\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6104DD-0F21-4802-9180-3D765A108675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401B16C4-463E-4D36-ABFC-BCEA9D592EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1741,7 +1741,9 @@
       <c r="W14" s="12">
         <v>0.2</v>
       </c>
-      <c r="X14" s="34"/>
+      <c r="X14" s="34">
+        <v>0.28000000000000003</v>
+      </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
@@ -2258,6 +2260,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010027BDBDF69F845F4383C93D67CEBAFF04" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0ea007cbf4cb5b5cc813a7650d64ca58">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb0b624f-ae06-4913-a28b-bf5d24a61ccb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8b65969171b7152b51da7f3e00aa75fb" ns2:_="">
     <xsd:import namespace="bb0b624f-ae06-4913-a28b-bf5d24a61ccb"/>
@@ -2401,35 +2418,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3153C880-55AF-461C-8404-BF1700CFFF35}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{202A6DEA-E6D4-40E2-A2D3-7299EF3E3732}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="bb0b624f-ae06-4913-a28b-bf5d24a61ccb"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2451,9 +2443,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{202A6DEA-E6D4-40E2-A2D3-7299EF3E3732}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3153C880-55AF-461C-8404-BF1700CFFF35}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="bb0b624f-ae06-4913-a28b-bf5d24a61ccb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>